--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.015982451498543</v>
+        <v>1.302597148368513</v>
       </c>
       <c r="D2" t="n">
-        <v>12.25909960730684</v>
+        <v>1.992103686187362</v>
       </c>
       <c r="E2" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F2" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.03445374154053</v>
+        <v>6.018098733000336</v>
       </c>
       <c r="D3" t="n">
-        <v>36.92720468771544</v>
+        <v>6.000670761753759</v>
       </c>
       <c r="E3" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F3" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.17965896269784</v>
+        <v>2.954194581438399</v>
       </c>
       <c r="D4" t="n">
-        <v>17.90891144862141</v>
+        <v>2.91019811040098</v>
       </c>
       <c r="E4" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F4" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.00030574595263</v>
+        <v>3.900049683717302</v>
       </c>
       <c r="D5" t="n">
-        <v>23.87544171959653</v>
+        <v>3.879759279434436</v>
       </c>
       <c r="E5" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F5" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.17321349390269</v>
+        <v>6.528147192759188</v>
       </c>
       <c r="D6" t="n">
-        <v>41.80847246046652</v>
+        <v>6.79387677482581</v>
       </c>
       <c r="E6" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F6" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.77544885177006</v>
+        <v>10.36351043841263</v>
       </c>
       <c r="D7" t="n">
-        <v>64.67433144558608</v>
+        <v>10.50957885990774</v>
       </c>
       <c r="E7" t="n">
-        <v>17.94409839138318</v>
+        <v>2.915915988599767</v>
       </c>
       <c r="F7" t="n">
-        <v>17.49956703640293</v>
+        <v>2.843679643415476</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
